--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.76341990002862</v>
+        <v>6.461555733754651</v>
       </c>
       <c r="D2" t="n">
-        <v>40.57933187796122</v>
+        <v>6.594141430168699</v>
       </c>
       <c r="E2" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F2" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.34951482633789</v>
+        <v>6.719296159279907</v>
       </c>
       <c r="D3" t="n">
-        <v>41.89806971630232</v>
+        <v>6.808436328899127</v>
       </c>
       <c r="E3" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F3" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.24021431838282</v>
+        <v>5.726534826737208</v>
       </c>
       <c r="D4" t="n">
-        <v>36.15733601567233</v>
+        <v>5.875567102546754</v>
       </c>
       <c r="E4" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F4" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.79213647410979</v>
+        <v>6.466222177042841</v>
       </c>
       <c r="D5" t="n">
-        <v>40.91388072599842</v>
+        <v>6.648505617974743</v>
       </c>
       <c r="E5" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F5" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.76758426273045</v>
+        <v>5.324732442693699</v>
       </c>
       <c r="D6" t="n">
-        <v>32.73909379742041</v>
+        <v>5.320102742080817</v>
       </c>
       <c r="E6" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F6" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.27489838228171</v>
+        <v>7.032170987120777</v>
       </c>
       <c r="D7" t="n">
-        <v>43.30681861874802</v>
+        <v>7.037358025546554</v>
       </c>
       <c r="E7" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F7" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.85592908264881</v>
+        <v>6.151588475930432</v>
       </c>
       <c r="D8" t="n">
-        <v>36.97887718570602</v>
+        <v>6.009067542677228</v>
       </c>
       <c r="E8" t="n">
-        <v>3.339046624235228</v>
+        <v>0.5425950764382246</v>
       </c>
       <c r="F8" t="n">
-        <v>3.473231276282488</v>
+        <v>0.5644000823959044</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
